--- a/data/trans_camb/IP19C02-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP19C02-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 4,56</t>
+          <t>-11,67; 4,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 21,55</t>
+          <t>-1,5; 21,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,09; 31,45</t>
+          <t>9,7; 31,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 22,74</t>
+          <t>1,03; 21,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 19,58</t>
+          <t>1,03; 20,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,86; 34,86</t>
+          <t>15,22; 34,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 9,12</t>
+          <t>-3,4; 9,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,59; 17,03</t>
+          <t>2,71; 16,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,11; 30,21</t>
+          <t>14,95; 29,31</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 167,02</t>
+          <t>-100,0; 178,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 490,06</t>
+          <t>-23,49; 669,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69,06; 912,83</t>
+          <t>59,62; 851,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 1496,95</t>
+          <t>-34,41; 1283,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-28,92; 1269,0</t>
+          <t>-26,81; 1178,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>150,3; 2491,36</t>
+          <t>133,77; 2642,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,47; 250,05</t>
+          <t>-48,37; 270,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,63; 455,0</t>
+          <t>26,28; 530,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>145,15; 865,41</t>
+          <t>130,43; 851,8</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 6,97</t>
+          <t>-8,74; 6,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 20,57</t>
+          <t>2,75; 22,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,3; 37,7</t>
+          <t>15,71; 38,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,5; 2,32</t>
+          <t>-20,11; 1,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 14,93</t>
+          <t>-10,03; 15,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 25,75</t>
+          <t>-0,49; 26,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 1,78</t>
+          <t>-10,49; 2,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 15,45</t>
+          <t>-0,18; 15,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,64; 28,76</t>
+          <t>10,62; 28,59</t>
         </is>
       </c>
     </row>
@@ -1004,42 +1004,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 1682,04</t>
+          <t>2,85; 1419,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>114,41; 2471,55</t>
+          <t>93,52; 2389,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-90,16; 83,39</t>
+          <t>-89,7; 50,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,74; 203,28</t>
+          <t>-49,32; 234,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 379,36</t>
+          <t>-10,36; 355,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-81,92; 52,04</t>
+          <t>-80,6; 68,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 271,33</t>
+          <t>-8,48; 270,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>72,44; 506,43</t>
+          <t>72,28; 540,68</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 5,67</t>
+          <t>-3,14; 5,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,96; 20,7</t>
+          <t>2,23; 20,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,4; 49,31</t>
+          <t>14,82; 48,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 11,45</t>
+          <t>-2,56; 11,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,52; 26,74</t>
+          <t>3,76; 25,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,75; 48,31</t>
+          <t>19,19; 48,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 5,67</t>
+          <t>-1,92; 6,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,67; 19,8</t>
+          <t>5,42; 19,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,08; 42,95</t>
+          <t>22,11; 45,12</t>
         </is>
       </c>
     </row>
@@ -1235,27 +1235,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-15,92; —</t>
+          <t>-5,49; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>213,47; —</t>
+          <t>257,5; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 767,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>63,17; 2509,66</t>
+          <t>96,24; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>420,29; 6781,98</t>
+          <t>423,5; 6708,55</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 7,05</t>
+          <t>-6,12; 7,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,65; 18,19</t>
+          <t>3,06; 17,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,65; 23,78</t>
+          <t>5,74; 24,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 7,97</t>
+          <t>-2,72; 8,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,46; 23,32</t>
+          <t>7,38; 23,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,22; 34,19</t>
+          <t>15,04; 33,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 5,48</t>
+          <t>-3,36; 5,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,36; 18,12</t>
+          <t>7,54; 18,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,84; 25,56</t>
+          <t>12,61; 25,4</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-52,44; 123,42</t>
+          <t>-52,91; 134,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14,97; 307,98</t>
+          <t>22,75; 340,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52,28; 432,46</t>
+          <t>39,8; 430,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-49,1; 331,45</t>
+          <t>-48,59; 360,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>102,03; 1056,51</t>
+          <t>83,34; 1068,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>184,52; 1447,76</t>
+          <t>166,46; 1435,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-35,55; 119,86</t>
+          <t>-40,76; 110,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>70,35; 347,79</t>
+          <t>82,35; 371,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>133,9; 499,18</t>
+          <t>130,01; 508,26</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,6; -0,14</t>
+          <t>-16,44; -0,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 18,84</t>
+          <t>-1,86; 19,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,7; 27,23</t>
+          <t>2,78; 27,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 2,53</t>
+          <t>-11,35; 2,6</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,74; 25,08</t>
+          <t>4,76; 25,34</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,81; 34,91</t>
+          <t>11,45; 35,55</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-10,51; -1,21</t>
+          <t>-11,33; -0,82</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,03; 19,19</t>
+          <t>5,16; 20,03</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12,18; 29,38</t>
+          <t>12,02; 29,45</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-87,5; 10,35</t>
+          <t>-89,3; 6,95</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-12,57; 294,99</t>
+          <t>-13,45; 278,4</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19,02; 393,85</t>
+          <t>13,98; 392,79</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-85,85; 72,91</t>
+          <t>-87,07; 71,57</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>36,03; 512,15</t>
+          <t>33,47; 503,45</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,88; 725,54</t>
+          <t>85,7; 694,35</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-79,93; -11,4</t>
+          <t>-80,2; -5,56</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>33,02; 264,85</t>
+          <t>31,24; 267,61</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>87,15; 404,91</t>
+          <t>81,82; 388,46</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 18,72</t>
+          <t>-3,26; 19,83</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>6,89; 34,55</t>
+          <t>7,02; 33,91</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25,58; 53,54</t>
+          <t>25,47; 54,03</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 3,32</t>
+          <t>-13,51; 3,52</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 27,59</t>
+          <t>0,89; 28,21</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,48; 59,56</t>
+          <t>25,46; 55,5</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 6,27</t>
+          <t>-5,75; 7,15</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>7,29; 26,89</t>
+          <t>7,47; 27,38</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>29,81; 49,97</t>
+          <t>30,16; 50,65</t>
         </is>
       </c>
     </row>
@@ -1863,17 +1863,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>30,46; 2308,88</t>
+          <t>26,15; 2357,25</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>238,67; 4304,55</t>
+          <t>193,07; 4101,86</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1883,27 +1883,27 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-23,11; 961,62</t>
+          <t>-21,17; 1086,71</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>146,83; 2328,0</t>
+          <t>159,44; 2507,22</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-81,88; 250,67</t>
+          <t>-74,49; 290,85</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>55,47; 826,06</t>
+          <t>65,96; 968,47</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>298,44; 1723,57</t>
+          <t>288,33; 1820,91</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 1,58</t>
+          <t>-4,57; 1,64</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>7,22; 15,52</t>
+          <t>7,27; 15,71</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>16,98; 26,32</t>
+          <t>17,11; 26,37</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 3,27</t>
+          <t>-2,7; 3,23</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>8,87; 16,94</t>
+          <t>8,66; 17,25</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,98; 29,82</t>
+          <t>20,12; 29,96</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 1,84</t>
+          <t>-2,72; 1,6</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>9,23; 15,1</t>
+          <t>9,0; 15,09</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>20,33; 27,12</t>
+          <t>20,58; 27,17</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-53,68; 29,0</t>
+          <t>-51,61; 27,51</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>76,15; 267,02</t>
+          <t>78,14; 275,19</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>180,88; 449,66</t>
+          <t>182,32; 462,41</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-38,39; 68,05</t>
+          <t>-35,89; 62,87</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>105,02; 352,79</t>
+          <t>104,22; 334,74</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>248,18; 621,39</t>
+          <t>251,02; 600,42</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-35,49; 32,77</t>
+          <t>-34,67; 29,27</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>111,85; 264,15</t>
+          <t>113,02; 276,38</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>242,03; 477,72</t>
+          <t>252,45; 483,01</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C02-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP19C02-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 4,29</t>
+          <t>-11,09; 5,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 21,56</t>
+          <t>-0,73; 22,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,7; 31,81</t>
+          <t>9,58; 31,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 21,32</t>
+          <t>0,85; 21,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 20,1</t>
+          <t>1,13; 19,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,22; 34,58</t>
+          <t>15,8; 35,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 9,74</t>
+          <t>-3,23; 9,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,71; 16,57</t>
+          <t>2,33; 17,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,95; 29,31</t>
+          <t>14,25; 29,17</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 178,89</t>
+          <t>-100,0; 352,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,49; 669,54</t>
+          <t>-22,59; 583,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59,62; 851,43</t>
+          <t>62,21; 814,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-34,41; 1283,72</t>
+          <t>-25,93; 1406,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-26,81; 1178,14</t>
+          <t>-16,37; 1716,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>133,77; 2642,59</t>
+          <t>121,43; 2450,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-48,37; 270,94</t>
+          <t>-42,93; 269,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,28; 530,89</t>
+          <t>17,59; 504,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>130,43; 851,8</t>
+          <t>139,8; 958,53</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 6,57</t>
+          <t>-7,53; 6,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,75; 22,35</t>
+          <t>1,73; 20,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,71; 38,38</t>
+          <t>15,79; 37,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,11; 1,79</t>
+          <t>-19,56; 1,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 15,39</t>
+          <t>-11,14; 14,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 26,83</t>
+          <t>-0,57; 24,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 2,75</t>
+          <t>-10,93; 2,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 15,37</t>
+          <t>-0,85; 15,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,62; 28,59</t>
+          <t>11,5; 28,29</t>
         </is>
       </c>
     </row>
@@ -1004,42 +1004,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,85; 1419,52</t>
+          <t>-1,33; 1221,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93,52; 2389,24</t>
+          <t>131,54; 3007,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-89,7; 50,93</t>
+          <t>-91,01; 50,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,32; 234,79</t>
+          <t>-53,65; 182,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 355,21</t>
+          <t>-6,21; 337,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-80,6; 68,25</t>
+          <t>-81,1; 49,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 270,81</t>
+          <t>-8,11; 278,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>72,28; 540,68</t>
+          <t>71,83; 483,36</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 5,97</t>
+          <t>-3,13; 5,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,23; 20,84</t>
+          <t>2,55; 22,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,82; 48,75</t>
+          <t>15,97; 46,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 11,07</t>
+          <t>-2,02; 11,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,76; 25,73</t>
+          <t>3,99; 24,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,19; 48,01</t>
+          <t>19,09; 49,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 6,64</t>
+          <t>-2,41; 5,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,42; 19,6</t>
+          <t>4,57; 19,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,11; 45,12</t>
+          <t>21,02; 42,27</t>
         </is>
       </c>
     </row>
@@ -1235,27 +1235,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-5,49; —</t>
+          <t>-5,21; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>257,5; —</t>
+          <t>223,13; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 985,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>96,24; —</t>
+          <t>43,04; 2764,97</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>423,5; 6708,55</t>
+          <t>445,97; 6496,61</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 7,63</t>
+          <t>-6,06; 8,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,06; 17,63</t>
+          <t>2,8; 17,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,74; 24,02</t>
+          <t>5,13; 23,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 8,39</t>
+          <t>-3,12; 7,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,38; 23,28</t>
+          <t>8,34; 22,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,04; 33,49</t>
+          <t>14,04; 33,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 5,58</t>
+          <t>-2,9; 6,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,54; 18,28</t>
+          <t>7,54; 18,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,61; 25,4</t>
+          <t>13,21; 25,57</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-52,91; 134,97</t>
+          <t>-55,11; 138,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>22,75; 340,6</t>
+          <t>14,27; 318,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39,8; 430,14</t>
+          <t>29,67; 360,3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-48,59; 360,25</t>
+          <t>-50,98; 319,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>83,34; 1068,32</t>
+          <t>83,57; 923,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>166,46; 1435,9</t>
+          <t>149,11; 1284,76</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-40,76; 110,54</t>
+          <t>-35,06; 137,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>82,35; 371,76</t>
+          <t>79,98; 381,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>130,01; 508,26</t>
+          <t>138,97; 525,34</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-16,44; -0,23</t>
+          <t>-16,4; -0,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 19,41</t>
+          <t>-1,2; 19,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,78; 27,22</t>
+          <t>4,08; 28,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 2,6</t>
+          <t>-12,21; 2,34</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,76; 25,34</t>
+          <t>5,5; 26,95</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,45; 35,55</t>
+          <t>10,69; 35,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-11,33; -0,82</t>
+          <t>-10,85; -0,89</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,16; 20,03</t>
+          <t>5,18; 19,59</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12,02; 29,45</t>
+          <t>11,3; 28,87</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-89,3; 6,95</t>
+          <t>-88,43; 0,38</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-13,45; 278,4</t>
+          <t>-14,2; 271,0</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13,98; 392,79</t>
+          <t>16,44; 389,91</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-87,07; 71,57</t>
+          <t>-87,17; 67,43</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>33,47; 503,45</t>
+          <t>38,52; 586,72</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,7; 694,35</t>
+          <t>76,22; 782,43</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-80,2; -5,56</t>
+          <t>-80,25; -5,06</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>31,24; 267,61</t>
+          <t>38,61; 276,06</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>81,82; 388,46</t>
+          <t>85,96; 407,44</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 19,83</t>
+          <t>-3,75; 18,46</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>7,02; 33,91</t>
+          <t>8,33; 34,3</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25,47; 54,03</t>
+          <t>26,64; 54,08</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-13,51; 3,52</t>
+          <t>-13,32; 3,44</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,89; 28,21</t>
+          <t>-0,4; 28,07</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,46; 55,5</t>
+          <t>25,6; 57,1</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 7,15</t>
+          <t>-6,02; 6,29</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>7,47; 27,38</t>
+          <t>7,17; 26,97</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>30,16; 50,65</t>
+          <t>30,13; 51,42</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>26,15; 2357,25</t>
+          <t>60,37; 2816,18</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>193,07; 4101,86</t>
+          <t>205,09; 3820,23</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1883,27 +1883,27 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-21,17; 1086,71</t>
+          <t>-18,31; 912,16</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>159,44; 2507,22</t>
+          <t>159,05; 2256,64</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-74,49; 290,85</t>
+          <t>-78,88; 249,28</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>65,96; 968,47</t>
+          <t>57,83; 894,15</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>288,33; 1820,91</t>
+          <t>292,96; 1861,57</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 1,64</t>
+          <t>-4,28; 1,84</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>7,27; 15,71</t>
+          <t>7,16; 15,62</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>17,11; 26,37</t>
+          <t>17,53; 26,51</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 3,23</t>
+          <t>-2,84; 3,26</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>8,66; 17,25</t>
+          <t>8,86; 17,1</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,12; 29,96</t>
+          <t>20,65; 30,41</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 1,6</t>
+          <t>-2,73; 1,5</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>9,0; 15,09</t>
+          <t>9,11; 15,09</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>20,58; 27,17</t>
+          <t>20,14; 26,79</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-51,61; 27,51</t>
+          <t>-47,97; 34,27</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>78,14; 275,19</t>
+          <t>75,29; 275,36</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>182,32; 462,41</t>
+          <t>202,17; 508,88</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-35,89; 62,87</t>
+          <t>-36,53; 67,74</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>104,22; 334,74</t>
+          <t>109,66; 368,24</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>251,02; 600,42</t>
+          <t>250,78; 650,47</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-34,67; 29,27</t>
+          <t>-35,03; 27,31</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>113,02; 276,38</t>
+          <t>107,76; 259,5</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>252,45; 483,01</t>
+          <t>240,83; 471,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C02-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP19C02-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10,47</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9,76</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>27,81</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-3,46</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>9,9</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>20,52</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10,47</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9,76</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,53</t>
+          <t>21,89</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>22,45</t>
+          <t>24,88</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 5,81</t>
+          <t>1,99; 22,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 22,0</t>
+          <t>1,05; 19,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,58; 31,19</t>
+          <t>18,78; 38,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 21,18</t>
+          <t>-11,16; 4,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 19,37</t>
+          <t>0,12; 21,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,8; 35,4</t>
+          <t>11,68; 33,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 9,67</t>
+          <t>-3,42; 9,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 17,27</t>
+          <t>2,59; 17,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,25; 29,17</t>
+          <t>17,11; 32,78</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>253,49%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>236,09%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>673,02%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-44,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>125,79%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>260,61%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>253,49%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>236,09%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>593,7%</t>
+          <t>278,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>367,97%</t>
+          <t>407,85%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 352,28</t>
+          <t>-5,35; 1496,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-22,59; 583,08</t>
+          <t>-28,92; 1269,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62,21; 814,09</t>
+          <t>186,33; 2750,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-25,93; 1406,74</t>
+          <t>-100,0; 167,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 1716,78</t>
+          <t>-13,61; 490,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>121,43; 2450,64</t>
+          <t>83,17; 964,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,93; 269,51</t>
+          <t>-41,47; 250,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,59; 504,53</t>
+          <t>17,63; 455,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>139,8; 958,53</t>
+          <t>160,44; 943,24</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-8,11</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,95</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>15,55</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-0,35</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>11,24</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>26,52</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-8,11</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,95</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,3</t>
+          <t>27,83</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>19,97</t>
+          <t>21,82</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 6,79</t>
+          <t>-18,5; 2,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,73; 20,86</t>
+          <t>-9,97; 14,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,79; 37,46</t>
+          <t>0,48; 28,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,56; 1,62</t>
+          <t>-8,36; 6,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 14,8</t>
+          <t>1,05; 20,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 24,53</t>
+          <t>17,64; 39,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 2,18</t>
+          <t>-11,68; 1,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 15,08</t>
+          <t>-0,01; 15,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,5; 28,29</t>
+          <t>12,28; 30,78</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-58,56%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21,28%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>112,26%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-7,24%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>230,47%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>543,93%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-58,56%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>21,28%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>570,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>217,97%</t>
+          <t>238,18%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>-90,16; 83,39</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>-52,74; 203,28</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>-3,48; 416,01</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-1,33; 1221,04</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>131,54; 3007,09</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-91,01; 50,08</t>
-        </is>
-      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-53,65; 182,6</t>
+          <t>-7,08; 1682,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 337,28</t>
+          <t>129,41; 2652,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-81,1; 49,54</t>
+          <t>-81,92; 52,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 278,49</t>
+          <t>-4,57; 271,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>71,83; 483,36</t>
+          <t>84,47; 544,93</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,85</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>12,68</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>33,4</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,32</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>9,97</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>29,63</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,85</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>12,68</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33,35</t>
+          <t>32,72</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>31,7</t>
+          <t>33,04</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 5,98</t>
+          <t>-2,35; 11,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,55; 22,16</t>
+          <t>3,52; 26,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,97; 46,74</t>
+          <t>19,52; 48,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 11,33</t>
+          <t>-3,17; 5,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,99; 24,9</t>
+          <t>1,96; 20,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,09; 49,67</t>
+          <t>16,91; 53,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 5,98</t>
+          <t>-1,96; 5,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,57; 19,15</t>
+          <t>4,67; 19,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,02; 42,27</t>
+          <t>22,23; 44,37</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>120,68%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>537,61%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1416,62%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>20,8%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>654,77%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1945,02%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>120,68%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>537,61%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1414,14%</t>
+          <t>2147,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1563,43%</t>
+          <t>1629,61%</t>
         </is>
       </c>
     </row>
@@ -1220,42 +1220,42 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>-15,92; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>222,02; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-5,21; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>223,13; —</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 985,52</t>
+          <t>-100,0; 767,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>43,04; 2764,97</t>
+          <t>63,17; 2509,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>445,97; 6496,61</t>
+          <t>434,92; 6918,34</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,13</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15,19</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>24,13</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,73</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>10,17</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>14,41</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,13</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>15,19</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,89</t>
+          <t>13,7</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>18,78</t>
+          <t>19,08</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 8,19</t>
+          <t>-3,26; 7,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,8; 17,95</t>
+          <t>8,46; 23,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,13; 23,28</t>
+          <t>16,15; 35,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 7,72</t>
+          <t>-6,01; 7,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,34; 22,77</t>
+          <t>2,65; 18,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,04; 33,16</t>
+          <t>6,12; 22,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 6,55</t>
+          <t>-2,83; 5,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,54; 18,06</t>
+          <t>7,36; 18,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,21; 25,57</t>
+          <t>12,96; 25,68</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>45,4%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>324,3%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>515,11%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>8,31%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>115,89%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>164,28%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>45,4%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>324,3%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>488,57%</t>
+          <t>156,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>278,2%</t>
+          <t>282,61%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-55,11; 138,82</t>
+          <t>-49,1; 331,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14,27; 318,99</t>
+          <t>102,03; 1056,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29,67; 360,3</t>
+          <t>197,81; 1524,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-50,98; 319,96</t>
+          <t>-52,44; 123,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>83,57; 923,73</t>
+          <t>14,97; 307,98</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>149,11; 1284,76</t>
+          <t>45,18; 421,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-35,06; 137,87</t>
+          <t>-35,55; 119,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>79,98; 381,51</t>
+          <t>70,35; 347,79</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>138,97; 525,34</t>
+          <t>135,36; 500,99</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-4,19</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>15,86</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>26,74</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-7,43</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>9,09</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>15,8</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-4,19</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>15,86</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,9</t>
+          <t>18,8</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>20,55</t>
+          <t>23,33</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-16,4; -0,57</t>
+          <t>-11,2; 2,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 19,93</t>
+          <t>5,74; 25,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,08; 28,37</t>
+          <t>13,38; 38,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-12,21; 2,34</t>
+          <t>-15,6; -0,14</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,5; 26,95</t>
+          <t>-1,9; 18,84</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,69; 35,92</t>
+          <t>6,53; 30,36</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-10,85; -0,89</t>
+          <t>-10,51; -1,21</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,18; 19,59</t>
+          <t>5,03; 19,19</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11,3; 28,87</t>
+          <t>15,37; 32,02</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-46,98%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>177,71%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>299,69%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-61,68%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>75,48%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>131,28%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-46,98%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>177,71%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>267,92%</t>
+          <t>156,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>199,74%</t>
+          <t>226,78%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-88,43; 0,38</t>
+          <t>-85,85; 72,91</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-14,2; 271,0</t>
+          <t>36,03; 512,15</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>16,44; 389,91</t>
+          <t>95,49; 780,57</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-87,17; 67,43</t>
+          <t>-87,5; 10,35</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>38,52; 586,72</t>
+          <t>-12,57; 294,99</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,22; 782,43</t>
+          <t>34,99; 433,82</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-80,25; -5,06</t>
+          <t>-79,93; -11,4</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>38,61; 276,06</t>
+          <t>33,02; 264,85</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>85,96; 407,44</t>
+          <t>107,11; 441,63</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-4,08</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>12,99</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>44,36</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>4,89</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>19,64</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>39,83</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-4,08</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>12,99</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>41,54</t>
+          <t>43,58</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>40,76</t>
+          <t>43,99</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 18,46</t>
+          <t>-13,42; 3,32</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>8,33; 34,3</t>
+          <t>-0,65; 27,59</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26,64; 54,08</t>
+          <t>29,25; 61,8</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 3,44</t>
+          <t>-3,2; 18,72</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 28,07</t>
+          <t>6,89; 34,55</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,6; 57,1</t>
+          <t>28,41; 57,0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 6,29</t>
+          <t>-6,2; 6,27</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>7,17; 26,97</t>
+          <t>7,29; 26,89</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>30,13; 51,42</t>
+          <t>32,89; 53,24</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-53,84%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>171,42%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>585,49%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>118,72%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>476,8%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>967,14%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-53,84%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>171,42%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>548,28%</t>
+          <t>1058,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>708,92%</t>
+          <t>764,98%</t>
         </is>
       </c>
     </row>
@@ -1868,42 +1868,42 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>60,37; 2816,18</t>
+          <t>-23,11; 961,62</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>205,09; 3820,23</t>
+          <t>160,74; 2336,32</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-18,31; 912,16</t>
+          <t>30,46; 2308,88</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>159,05; 2256,64</t>
+          <t>270,58; 4600,12</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-78,88; 249,28</t>
+          <t>-81,88; 250,67</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>57,83; 894,15</t>
+          <t>55,47; 826,06</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>292,96; 1861,57</t>
+          <t>327,78; 1795,9</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0,17</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>12,75</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>27,28</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-1,44</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>11,24</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>21,97</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>12,75</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,06</t>
+          <t>23,59</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>23,64</t>
+          <t>25,55</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 1,84</t>
+          <t>-3,07; 3,27</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>7,16; 15,62</t>
+          <t>8,87; 16,94</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>17,53; 26,51</t>
+          <t>22,2; 32,13</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 3,26</t>
+          <t>-4,79; 1,58</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>8,86; 17,1</t>
+          <t>7,22; 15,52</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,65; 30,41</t>
+          <t>18,58; 27,86</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 1,5</t>
+          <t>-2,77; 1,84</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>9,11; 15,09</t>
+          <t>9,23; 15,1</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>20,14; 26,79</t>
+          <t>22,22; 29,1</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>198,99%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>425,86%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-19,69%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>153,43%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>300,0%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>198,99%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>391,17%</t>
+          <t>322,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>345,05%</t>
+          <t>372,96%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-47,97; 34,27</t>
+          <t>-38,39; 68,05</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>75,29; 275,36</t>
+          <t>105,02; 352,79</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>202,17; 508,88</t>
+          <t>275,22; 667,68</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-36,53; 67,74</t>
+          <t>-53,68; 29,0</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>109,66; 368,24</t>
+          <t>76,15; 267,02</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>250,78; 650,47</t>
+          <t>197,29; 480,06</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-35,03; 27,31</t>
+          <t>-35,49; 32,77</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>107,76; 259,5</t>
+          <t>111,85; 264,15</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>240,83; 471,29</t>
+          <t>266,81; 514,09</t>
         </is>
       </c>
     </row>
